--- a/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
+++ b/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
@@ -2178,100 +2178,100 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="b">
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2303,16 +2303,16 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2324,22 +2324,22 @@
         <v>2</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -2360,13 +2360,13 @@
         <v>2</v>
       </c>
       <c r="Z13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="b">
         <v>0</v>
@@ -2387,13 +2387,13 @@
         <v>2</v>
       </c>
       <c r="AI13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
         <v>1</v>
@@ -2446,22 +2446,22 @@
         <v>2</v>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -2476,19 +2476,19 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
@@ -2497,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="AE14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
@@ -2509,13 +2509,13 @@
         <v>2</v>
       </c>
       <c r="AI14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="b">
         <v>1</v>
@@ -2547,43 +2547,43 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2598,19 +2598,19 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="b">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         <v>2</v>
       </c>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="b">
         <v>1</v>
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -2690,22 +2690,22 @@
         <v>2</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -2726,13 +2726,13 @@
         <v>2</v>
       </c>
       <c r="Z16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="b">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>2</v>
       </c>
       <c r="AI16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="b">
         <v>1</v>
@@ -2791,16 +2791,16 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2812,22 +2812,22 @@
         <v>2</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -2848,40 +2848,40 @@
         <v>2</v>
       </c>
       <c r="Z17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="b">
         <v>1</v>
@@ -2907,49 +2907,49 @@
         <v>1</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -2964,46 +2964,46 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
         <v>1</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -3056,22 +3056,22 @@
         <v>2</v>
       </c>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -3086,19 +3086,19 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="b">
         <v>0</v>
@@ -3119,13 +3119,13 @@
         <v>2</v>
       </c>
       <c r="AI19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="b">
         <v>1</v>
@@ -3151,22 +3151,22 @@
         <v>1</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3178,22 +3178,22 @@
         <v>2</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -3214,22 +3214,22 @@
         <v>2</v>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
@@ -3241,13 +3241,13 @@
         <v>2</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="b">
         <v>1</v>
@@ -3279,16 +3279,16 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3300,22 +3300,22 @@
         <v>2</v>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -3336,40 +3336,40 @@
         <v>2</v>
       </c>
       <c r="Z21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="b">
         <v>1</v>
@@ -3398,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -3422,22 +3422,22 @@
         <v>2</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -3458,22 +3458,22 @@
         <v>2</v>
       </c>
       <c r="Z22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="b">
         <v>0</v>
@@ -3485,13 +3485,13 @@
         <v>2</v>
       </c>
       <c r="AI22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
         <v>1</v>
@@ -3526,13 +3526,13 @@
         <v>2</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -3544,22 +3544,22 @@
         <v>2</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>2</v>
       </c>
       <c r="Z23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="AE23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="AI23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="b">
         <v>1</v>
@@ -3639,103 +3639,103 @@
         <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
         <v>1</v>
@@ -3773,55 +3773,55 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
@@ -3836,19 +3836,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3958,19 +3958,19 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4026,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -4166,28 +4166,28 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
@@ -4270,10 +4270,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -4306,10 +4306,10 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
@@ -4324,19 +4324,19 @@
         <v>0</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="b">
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4383,19 +4383,19 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -4419,19 +4419,19 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W30" t="b">
         <v>0</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
@@ -4446,19 +4446,19 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF30" t="b">
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4496,64 +4496,64 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
       <c r="R31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W31" t="b">
         <v>0</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
@@ -4568,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
       </c>
       <c r="AG31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4618,64 +4618,64 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
       <c r="R32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
       </c>
       <c r="U32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W32" t="b">
         <v>0</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
@@ -4690,28 +4690,28 @@
         <v>0</v>
       </c>
       <c r="AD32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF32" t="b">
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL32" t="b">
         <v>1</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4767,37 +4767,37 @@
         <v>0</v>
       </c>
       <c r="O33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W33" t="b">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -4812,28 +4812,28 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL33" t="b">
         <v>1</v>
@@ -4862,64 +4862,64 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
       <c r="R34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W34" t="b">
         <v>0</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z34" t="b">
         <v>0</v>
@@ -4934,28 +4934,28 @@
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>
       </c>
       <c r="AG34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL34" t="b">
         <v>1</v>
@@ -5011,19 +5011,19 @@
         <v>0</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
       <c r="R35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
@@ -5065,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5106,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -5124,37 +5124,37 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
       </c>
       <c r="O36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
       <c r="R36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W36" t="b">
         <v>0</v>
@@ -5187,10 +5187,10 @@
         <v>0</v>
       </c>
       <c r="AG36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5237,46 +5237,46 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="b">
         <v>0</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W37" t="b">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5368,37 +5368,37 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="b">
         <v>0</v>
       </c>
       <c r="U38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W38" t="b">
         <v>0</v>
@@ -5431,10 +5431,10 @@
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5472,46 +5472,46 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
       <c r="R39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
@@ -5544,19 +5544,19 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF39" t="b">
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5621,19 +5621,19 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
       <c r="R40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="b">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
       <c r="R41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="b">
         <v>0</v>
@@ -5865,28 +5865,28 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
       <c r="U42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" t="b">
         <v>0</v>
@@ -5919,10 +5919,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -5978,28 +5978,28 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T43" t="b">
         <v>0</v>
@@ -6041,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6085,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="P44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="S44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="V44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W44" t="b">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="b">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="AE44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="b">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="AH44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="AK44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL44" t="b">
         <v>1</v>
@@ -6207,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>1</v>
       </c>
       <c r="P45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="S45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T45" t="b">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>1</v>
       </c>
       <c r="V45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W45" t="b">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="b">
         <v>0</v>
@@ -6270,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="b">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="AE45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
@@ -6288,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="AH45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6297,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="AK45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL45" t="b">
         <v>1</v>
@@ -6356,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
@@ -6392,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC46" t="b">
         <v>0</v>
@@ -6478,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>1</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="b">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="P48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="AB48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="b">
         <v>0</v>
@@ -6722,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="P49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>1</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="b">
         <v>0</v>
@@ -6844,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -6880,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC50" t="b">
         <v>0</v>
@@ -6966,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="P51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -7002,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC51" t="b">
         <v>0</v>
@@ -7058,100 +7058,100 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T52" t="b">
         <v>0</v>
       </c>
       <c r="U52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="W52" t="b">
         <v>0</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="b">
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AC52" t="b">
         <v>0</v>
       </c>
       <c r="AD52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
       </c>
       <c r="AJ52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AL52" t="b">
         <v>1</v>

--- a/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
+++ b/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="155">
   <si>
     <t>SKU</t>
   </si>
@@ -136,9 +136,6 @@
     <t>HQ_Max</t>
   </si>
   <si>
-    <t>29560</t>
-  </si>
-  <si>
     <t>29247</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>10395</t>
   </si>
   <si>
-    <t>29559</t>
-  </si>
-  <si>
     <t>10396</t>
   </si>
   <si>
@@ -301,7 +295,7 @@
     <t>29746</t>
   </si>
   <si>
-    <t>BBB Dipped Cow Ear Apple Cinnamon SEAS</t>
+    <t>15500</t>
   </si>
   <si>
     <t>BBB Dipped Cow Ear Bacon</t>
@@ -319,9 +313,6 @@
     <t>BBB Dipped Cow Ear PB</t>
   </si>
   <si>
-    <t>BBB Dipped Cow Ear Pumpkin Spice SEAS</t>
-  </si>
-  <si>
     <t>BBB Dipped Cow Ear Smoked</t>
   </si>
   <si>
@@ -464,6 +455,9 @@
   </si>
   <si>
     <t>Wee-wee Disposable Diapers MD 12ct</t>
+  </si>
+  <si>
+    <t>Bitter Apple 8-oz</t>
   </si>
   <si>
     <t>Bradley Caldwell</t>
@@ -816,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -946,10 +940,10 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -1068,10 +1062,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -1116,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="S3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -1190,10 +1184,10 @@
         <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -1312,10 +1306,10 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D5">
         <v>25</v>
@@ -1434,10 +1428,10 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -1556,10 +1550,10 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -1678,10 +1672,10 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8">
         <v>25</v>
@@ -1800,10 +1794,10 @@
         <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D9">
         <v>25</v>
@@ -1812,100 +1806,100 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="V9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AB9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="b">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -1922,112 +1916,112 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AK10">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="b">
         <v>1</v>
@@ -2044,112 +2038,112 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -2166,10 +2160,10 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2178,100 +2172,100 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="b">
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2288,10 +2282,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2318,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -2354,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="b">
         <v>1</v>
@@ -2410,10 +2404,10 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2422,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -2479,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="b">
         <v>1</v>
@@ -2497,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="AE14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
@@ -2532,10 +2526,10 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2562,10 +2556,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -2598,10 +2592,10 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="b">
         <v>1</v>
@@ -2613,22 +2607,22 @@
         <v>0</v>
       </c>
       <c r="AC15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2654,77 +2648,77 @@
         <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
         <v>4</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>2</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16">
-        <v>2</v>
-      </c>
       <c r="Z16" t="b">
         <v>1</v>
       </c>
@@ -2735,22 +2729,22 @@
         <v>0</v>
       </c>
       <c r="AC16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2776,10 +2770,10 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2788,19 +2782,19 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2842,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="b">
         <v>1</v>
@@ -2869,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2898,10 +2892,10 @@
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2928,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -2964,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="b">
         <v>1</v>
@@ -2991,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="b">
         <v>1</v>
@@ -3020,10 +3014,10 @@
         <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3032,19 +3026,19 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3086,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="b">
         <v>1</v>
@@ -3101,22 +3095,22 @@
         <v>0</v>
       </c>
       <c r="AC19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3142,31 +3136,31 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3205,13 +3199,13 @@
         <v>2</v>
       </c>
       <c r="W20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="b">
         <v>1</v>
@@ -3264,10 +3258,10 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3279,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -3327,13 +3321,13 @@
         <v>2</v>
       </c>
       <c r="W21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="b">
         <v>1</v>
@@ -3345,22 +3339,22 @@
         <v>0</v>
       </c>
       <c r="AC21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3386,40 +3380,40 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -3440,22 +3434,22 @@
         <v>0</v>
       </c>
       <c r="T22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="b">
         <v>1</v>
@@ -3476,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="AF22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3508,10 +3502,10 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3526,94 +3520,94 @@
         <v>2</v>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="b">
         <v>1</v>
@@ -3630,112 +3624,112 @@
         <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="b">
         <v>1</v>
@@ -3752,10 +3746,10 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3773,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3785,16 +3779,16 @@
         <v>2</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3803,26 +3797,26 @@
         <v>3</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V25">
+        <v>2</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>3</v>
+      </c>
+      <c r="Y25">
         <v>5</v>
       </c>
-      <c r="W25" t="b">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>2</v>
-      </c>
-      <c r="Y25">
-        <v>4</v>
-      </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
@@ -3836,19 +3830,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3874,10 +3868,10 @@
         <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3895,55 +3889,55 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>3</v>
+      </c>
+      <c r="S26">
+        <v>5</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>2</v>
+      </c>
+      <c r="V26">
         <v>4</v>
       </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>2</v>
-      </c>
-      <c r="P26">
-        <v>3</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>3</v>
-      </c>
-      <c r="S26">
-        <v>4</v>
-      </c>
-      <c r="T26" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>2</v>
-      </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -3958,19 +3952,19 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -3996,10 +3990,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4044,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -4062,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
@@ -4080,19 +4074,19 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4118,10 +4112,10 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4139,19 +4133,19 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -4166,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4202,19 +4196,19 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4240,10 +4234,10 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4252,91 +4246,91 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W29" t="b">
         <v>0</v>
       </c>
       <c r="X29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y29">
+        <v>5</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>2</v>
+      </c>
+      <c r="AB29">
+        <v>3</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>3</v>
+      </c>
+      <c r="AE29">
+        <v>5</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>3</v>
+      </c>
+      <c r="AH29">
         <v>4</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>1</v>
-      </c>
-      <c r="AB29">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>2</v>
-      </c>
-      <c r="AE29">
-        <v>4</v>
-      </c>
-      <c r="AF29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>2</v>
-      </c>
-      <c r="AH29">
-        <v>3</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4362,10 +4356,10 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4374,19 +4368,19 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4401,19 +4395,19 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
       <c r="R30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -4437,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC30" t="b">
         <v>0</v>
@@ -4455,19 +4449,19 @@
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="b">
         <v>1</v>
@@ -4484,10 +4478,10 @@
         <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4514,10 +4508,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -4532,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -4550,28 +4544,28 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y31">
+        <v>5</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>2</v>
+      </c>
+      <c r="AB31">
+        <v>3</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>2</v>
+      </c>
+      <c r="AE31">
         <v>4</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>1</v>
-      </c>
-      <c r="AB31">
-        <v>2</v>
-      </c>
-      <c r="AC31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>3</v>
-      </c>
-      <c r="AE31">
-        <v>5</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
@@ -4586,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="b">
         <v>1</v>
@@ -4606,10 +4600,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4618,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -4636,10 +4630,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -4654,10 +4648,10 @@
         <v>0</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -4681,10 +4675,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC32" t="b">
         <v>0</v>
@@ -4693,16 +4687,16 @@
         <v>2</v>
       </c>
       <c r="AE32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF32" t="b">
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4728,10 +4722,10 @@
         <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4740,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -4752,7 +4746,7 @@
         <v>2</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4785,55 +4779,55 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V33">
+        <v>3</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>3</v>
+      </c>
+      <c r="Y33">
         <v>5</v>
       </c>
-      <c r="W33" t="b">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>2</v>
-      </c>
-      <c r="Y33">
-        <v>4</v>
-      </c>
       <c r="Z33" t="b">
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC33" t="b">
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="b">
         <v>1</v>
@@ -4850,10 +4844,10 @@
         <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4871,46 +4865,46 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>2</v>
+      </c>
+      <c r="P34">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>3</v>
+      </c>
+      <c r="S34">
         <v>5</v>
       </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>2</v>
-      </c>
-      <c r="M34">
-        <v>3</v>
-      </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>2</v>
-      </c>
-      <c r="P34">
-        <v>3</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>4</v>
-      </c>
-      <c r="S34">
-        <v>6</v>
-      </c>
       <c r="T34" t="b">
         <v>0</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W34" t="b">
         <v>0</v>
@@ -4934,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>
@@ -4952,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL34" t="b">
         <v>1</v>
@@ -4972,10 +4966,10 @@
         <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -4993,19 +4987,19 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -5020,46 +5014,46 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" t="b">
         <v>0</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z35" t="b">
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="b">
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF35" t="b">
         <v>0</v>
@@ -5094,10 +5088,10 @@
         <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5106,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -5124,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -5142,10 +5136,10 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
@@ -5160,10 +5154,10 @@
         <v>0</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="b">
         <v>0</v>
@@ -5178,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF36" t="b">
         <v>0</v>
@@ -5216,10 +5210,10 @@
         <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5228,19 +5222,19 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5264,10 +5258,10 @@
         <v>0</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="b">
         <v>0</v>
@@ -5282,37 +5276,37 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="b">
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC37" t="b">
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF37" t="b">
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5338,10 +5332,10 @@
         <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -5386,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="b">
         <v>0</v>
@@ -5404,10 +5398,10 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="b">
         <v>0</v>
@@ -5422,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF38" t="b">
         <v>0</v>
@@ -5460,10 +5454,10 @@
         <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -5472,91 +5466,91 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="P39">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>3</v>
+      </c>
+      <c r="S39">
         <v>5</v>
       </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>3</v>
-      </c>
-      <c r="M39">
-        <v>4</v>
-      </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>2</v>
-      </c>
-      <c r="P39">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>2</v>
-      </c>
-      <c r="S39">
-        <v>3</v>
-      </c>
       <c r="T39" t="b">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W39" t="b">
         <v>0</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z39" t="b">
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC39" t="b">
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF39" t="b">
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5582,10 +5576,10 @@
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5603,19 +5597,19 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -5630,46 +5624,46 @@
         <v>0</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="b">
         <v>0</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" t="b">
         <v>0</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="b">
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC40" t="b">
         <v>0</v>
       </c>
       <c r="AD40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF40" t="b">
         <v>0</v>
@@ -5704,10 +5698,10 @@
         <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5725,19 +5719,19 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -5752,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="b">
         <v>0</v>
@@ -5770,37 +5764,37 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="b">
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="b">
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF41" t="b">
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -5826,10 +5820,10 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -5841,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -5859,34 +5853,34 @@
         <v>1</v>
       </c>
       <c r="M42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
       </c>
       <c r="O42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W42" t="b">
         <v>0</v>
@@ -5895,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="Y42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
@@ -5904,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="b">
         <v>0</v>
@@ -5913,16 +5907,16 @@
         <v>1</v>
       </c>
       <c r="AE42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="b">
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -5931,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="b">
         <v>1</v>
@@ -5948,10 +5942,10 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -5963,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -5978,28 +5972,28 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
       </c>
       <c r="O43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T43" t="b">
         <v>0</v>
@@ -6008,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W43" t="b">
         <v>0</v>
@@ -6017,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="Y43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="b">
         <v>0</v>
@@ -6026,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="b">
         <v>0</v>
@@ -6035,16 +6029,16 @@
         <v>1</v>
       </c>
       <c r="AE43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF43" t="b">
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6053,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="AK43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL43" t="b">
         <v>1</v>
@@ -6070,10 +6064,10 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -6085,25 +6079,25 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -6112,61 +6106,61 @@
         <v>1</v>
       </c>
       <c r="P44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
       <c r="R44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
       </c>
       <c r="U44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W44" t="b">
         <v>0</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC44" t="b">
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF44" t="b">
         <v>0</v>
       </c>
       <c r="AG44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6175,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="AK44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL44" t="b">
         <v>1</v>
@@ -6192,10 +6186,10 @@
         <v>83</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -6207,25 +6201,25 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -6234,61 +6228,61 @@
         <v>1</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
       <c r="R45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T45" t="b">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W45" t="b">
         <v>0</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="b">
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC45" t="b">
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
       </c>
       <c r="AG45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6297,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="AK45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL45" t="b">
         <v>1</v>
@@ -6314,10 +6308,10 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -6335,19 +6329,19 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -6356,61 +6350,61 @@
         <v>1</v>
       </c>
       <c r="P46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
       <c r="R46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T46" t="b">
         <v>0</v>
       </c>
       <c r="U46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" t="b">
         <v>0</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="b">
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC46" t="b">
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF46" t="b">
         <v>0</v>
       </c>
       <c r="AG46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6436,10 +6430,10 @@
         <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6457,19 +6451,19 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -6478,61 +6472,61 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
       <c r="R47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T47" t="b">
         <v>0</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W47" t="b">
         <v>0</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="b">
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC47" t="b">
         <v>0</v>
       </c>
       <c r="AD47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
       </c>
       <c r="AG47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6558,10 +6552,10 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6579,19 +6573,19 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -6600,61 +6594,61 @@
         <v>1</v>
       </c>
       <c r="P48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T48" t="b">
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W48" t="b">
         <v>0</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="b">
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC48" t="b">
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
       </c>
       <c r="AG48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -6680,10 +6674,10 @@
         <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6701,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -6722,16 +6716,16 @@
         <v>1</v>
       </c>
       <c r="P49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
       <c r="R49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
@@ -6758,7 +6752,7 @@
         <v>1</v>
       </c>
       <c r="AB49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="b">
         <v>0</v>
@@ -6802,112 +6796,112 @@
         <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T50" t="b">
         <v>0</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="W50" t="b">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="b">
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB50">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC50" t="b">
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
       </c>
       <c r="AJ50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AL50" t="b">
         <v>1</v>
@@ -6924,7 +6918,7 @@
         <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
         <v>154</v>
@@ -6966,7 +6960,7 @@
         <v>1</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -6975,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T51" t="b">
         <v>0</v>
@@ -7002,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="AB51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="b">
         <v>0</v>
@@ -7046,112 +7040,112 @@
         <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
       <c r="R52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S52">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T52" t="b">
         <v>0</v>
       </c>
       <c r="U52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W52" t="b">
         <v>0</v>
       </c>
       <c r="X52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="b">
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="b">
         <v>0</v>
       </c>
       <c r="AD52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
       </c>
       <c r="AJ52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AL52" t="b">
         <v>1</v>
@@ -7168,10 +7162,10 @@
         <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7219,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="S53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" t="b">
         <v>0</v>
@@ -7290,10 +7284,10 @@
         <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7341,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="S54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T54" t="b">
         <v>0</v>
@@ -7412,10 +7406,10 @@
         <v>93</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7424,100 +7418,100 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
       </c>
       <c r="O55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
       <c r="R55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="b">
         <v>0</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W55" t="b">
         <v>0</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC55" t="b">
         <v>0</v>
       </c>
       <c r="AD55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF55" t="b">
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI55" t="b">
         <v>0</v>
       </c>
       <c r="AJ55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL55" t="b">
         <v>1</v>
@@ -7526,128 +7520,6 @@
         <v>0</v>
       </c>
       <c r="AN55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:40">
-      <c r="A56" t="s">
-        <v>94</v>
-      </c>
-      <c r="B56" t="s">
-        <v>149</v>
-      </c>
-      <c r="C56" t="s">
-        <v>156</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56">
-        <v>2</v>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>1</v>
-      </c>
-      <c r="M56">
-        <v>2</v>
-      </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="P56">
-        <v>2</v>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>1</v>
-      </c>
-      <c r="S56">
-        <v>2</v>
-      </c>
-      <c r="T56" t="b">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>1</v>
-      </c>
-      <c r="V56">
-        <v>2</v>
-      </c>
-      <c r="W56" t="b">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56">
-        <v>2</v>
-      </c>
-      <c r="Z56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>1</v>
-      </c>
-      <c r="AB56">
-        <v>2</v>
-      </c>
-      <c r="AC56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>1</v>
-      </c>
-      <c r="AE56">
-        <v>2</v>
-      </c>
-      <c r="AF56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56">
-        <v>1</v>
-      </c>
-      <c r="AH56">
-        <v>2</v>
-      </c>
-      <c r="AI56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ56">
-        <v>1</v>
-      </c>
-      <c r="AK56">
-        <v>2</v>
-      </c>
-      <c r="AL56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
         <v>0</v>
       </c>
     </row>

--- a/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
+++ b/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
@@ -1042,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="b">
         <v>1</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="b">
         <v>1</v>
@@ -1196,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -1214,82 +1214,82 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="V4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AB4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="b">
         <v>1</v>
@@ -1318,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -1336,82 +1336,82 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="V5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AB5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AC5" t="b">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="b">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>25</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="b">
         <v>1</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="b">
         <v>1</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -1702,82 +1702,82 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="V8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AB8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AK8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="b">
         <v>1</v>
@@ -1800,43 +1800,43 @@
         <v>148</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1851,16 +1851,16 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>25</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="b">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>25</v>
@@ -1887,19 +1887,19 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -1964,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1982,10 +1982,10 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -3830,10 +3830,10 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
@@ -3916,10 +3916,10 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3952,10 +3952,10 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
@@ -4038,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -4074,10 +4074,10 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
@@ -4404,10 +4404,10 @@
         <v>0</v>
       </c>
       <c r="R30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
@@ -4526,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -4544,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
@@ -4648,10 +4648,10 @@
         <v>0</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -4666,10 +4666,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
@@ -5844,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6808,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G50">
         <v>12</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J50">
         <v>12</v>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50">
         <v>12</v>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P50">
         <v>12</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="R50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S50">
         <v>12</v>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V50">
         <v>12</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="X50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y50">
         <v>12</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB50">
         <v>12</v>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH50">
         <v>12</v>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="AJ50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK50">
         <v>12</v>

--- a/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
+++ b/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="156">
   <si>
     <t>SKU</t>
   </si>
@@ -136,6 +136,9 @@
     <t>HQ_Max</t>
   </si>
   <si>
+    <t>Total Max</t>
+  </si>
+  <si>
     <t>29247</t>
   </si>
   <si>
@@ -163,6 +166,9 @@
     <t>12468</t>
   </si>
   <si>
+    <t>15500</t>
+  </si>
+  <si>
     <t>27913</t>
   </si>
   <si>
@@ -196,7 +202,7 @@
     <t>13262</t>
   </si>
   <si>
-    <t>13263</t>
+    <t>14289</t>
   </si>
   <si>
     <t>15291</t>
@@ -256,10 +262,13 @@
     <t>14785</t>
   </si>
   <si>
+    <t>29403</t>
+  </si>
+  <si>
     <t>29404</t>
   </si>
   <si>
-    <t>29403</t>
+    <t>13765</t>
   </si>
   <si>
     <t>29458</t>
@@ -280,24 +289,18 @@
     <t>29455</t>
   </si>
   <si>
-    <t>13765</t>
-  </si>
-  <si>
     <t>29747</t>
   </si>
   <si>
+    <t>29746</t>
+  </si>
+  <si>
     <t>29745</t>
   </si>
   <si>
     <t>29744</t>
   </si>
   <si>
-    <t>29746</t>
-  </si>
-  <si>
-    <t>15500</t>
-  </si>
-  <si>
     <t>BBB Dipped Cow Ear Bacon</t>
   </si>
   <si>
@@ -325,6 +328,9 @@
     <t>Bitter Apple 16-oz</t>
   </si>
   <si>
+    <t>Bitter Apple 8-oz</t>
+  </si>
+  <si>
     <t>Canidae ALS Chicken &amp; Rice 27lb</t>
   </si>
   <si>
@@ -358,7 +364,7 @@
     <t>Canidae Pure Lamb &amp; SwP 22lb</t>
   </si>
   <si>
-    <t>Canidae Pure Meadow Senior 22-lb</t>
+    <t>Canidae Pure Lamb &amp; SwP 4lb</t>
   </si>
   <si>
     <t>Fruitables Apple 7-oz</t>
@@ -418,10 +424,13 @@
     <t>Fruitables Skinny Minis Mango 5-oz</t>
   </si>
   <si>
+    <t>K&amp;H Window Mount Bed Kitty Face</t>
+  </si>
+  <si>
     <t>K&amp;H WIndow Mount Lounger w/ grass</t>
   </si>
   <si>
-    <t>K&amp;H Window Mount Bed Kitty Face</t>
+    <t>Pet Corrector 30ml</t>
   </si>
   <si>
     <t>PS Kaleidoscope 2 Knot Rope 10"</t>
@@ -442,24 +451,18 @@
     <t>PS Kingpin Kibbler 6"</t>
   </si>
   <si>
-    <t>Pet Corrector 30ml</t>
-  </si>
-  <si>
     <t>Wee-Wee Disposable Diapers LG/XL 12ct</t>
   </si>
   <si>
+    <t>Wee-wee Disposable Diapers MD 12ct</t>
+  </si>
+  <si>
     <t>Wee-Wee Disposable Diapers SM 12ct</t>
   </si>
   <si>
     <t>Wee-Wee Disposable Diapers XS 12ct</t>
   </si>
   <si>
-    <t>Wee-wee Disposable Diapers MD 12ct</t>
-  </si>
-  <si>
-    <t>Bitter Apple 8-oz</t>
-  </si>
-  <si>
     <t>Bradley Caldwell</t>
   </si>
   <si>
@@ -472,10 +475,10 @@
     <t>Fruitables</t>
   </si>
   <si>
+    <t>Pet Corrector</t>
+  </si>
+  <si>
     <t>Petsport</t>
-  </si>
-  <si>
-    <t>Pet Corrector</t>
   </si>
   <si>
     <t>Wee-Wee</t>
@@ -810,10 +813,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -934,16 +937,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -1056,16 +1062,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>525</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -1178,16 +1187,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>575</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -1300,16 +1312,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>300</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D5">
         <v>25</v>
@@ -1422,16 +1437,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>300</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -1544,16 +1562,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>525</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -1666,16 +1687,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>525</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D8">
         <v>25</v>
@@ -1788,16 +1812,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>300</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9">
         <v>20</v>
@@ -1842,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S9">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1860,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1878,10 +1905,10 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
@@ -1910,16 +1937,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>240</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2032,13 +2062,16 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>30</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -2050,100 +2083,100 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -2154,16 +2187,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>33</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2175,16 +2211,16 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2223,13 +2259,13 @@
         <v>2</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="b">
         <v>1</v>
@@ -2276,16 +2312,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2297,25 +2336,25 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -2345,13 +2384,13 @@
         <v>2</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="b">
         <v>1</v>
@@ -2398,16 +2437,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2416,1093 +2458,1120 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
         <v>4</v>
       </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>2</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>2</v>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>2</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>2</v>
-      </c>
-      <c r="Y14">
-        <v>3</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>1</v>
-      </c>
-      <c r="AE14">
-        <v>2</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>1</v>
-      </c>
-      <c r="AH14">
-        <v>2</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>2</v>
+      </c>
+      <c r="Y15">
+        <v>3</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>2</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15">
-        <v>3</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
+    <row r="16" spans="1:41">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>2</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>2</v>
-      </c>
-      <c r="Y16">
+    <row r="17" spans="1:41">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>2</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17">
         <v>4</v>
       </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>2</v>
+      </c>
+      <c r="AH17">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
-      </c>
-      <c r="V17">
-        <v>2</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>2</v>
-      </c>
-      <c r="Y17">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>1</v>
-      </c>
-      <c r="AH17">
-        <v>2</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
+    <row r="18" spans="1:41">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>3</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>2</v>
+      </c>
+      <c r="Y18">
+        <v>3</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>2</v>
+      </c>
+      <c r="AI18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>2</v>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>1</v>
-      </c>
-      <c r="V18">
-        <v>2</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>2</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>1</v>
-      </c>
-      <c r="AH18">
-        <v>2</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
+    <row r="19" spans="1:41">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>2</v>
+      </c>
+      <c r="AI19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>2</v>
-      </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19">
-        <v>2</v>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>3</v>
-      </c>
-      <c r="AH19">
+    <row r="20" spans="1:41">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>2</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>3</v>
+      </c>
+      <c r="AH20">
         <v>4</v>
       </c>
-      <c r="AI19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
+      <c r="AI20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>2</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>2</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20">
-        <v>2</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>2</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
+    <row r="21" spans="1:41">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>2</v>
+      </c>
+      <c r="AI21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21">
-        <v>2</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>1</v>
-      </c>
-      <c r="AH21">
-        <v>2</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
+    <row r="22" spans="1:41">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>2</v>
+      </c>
+      <c r="AI22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22" t="b">
-        <v>1</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>151</v>
@@ -3514,120 +3583,123 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>2</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
         <v>5</v>
       </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>3</v>
-      </c>
-      <c r="V23">
-        <v>5</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>3</v>
-      </c>
-      <c r="Y23">
-        <v>5</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>2</v>
-      </c>
-      <c r="AB23">
-        <v>3</v>
-      </c>
-      <c r="AC23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>3</v>
-      </c>
-      <c r="AE23">
-        <v>5</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>3</v>
-      </c>
-      <c r="AH23">
-        <v>4</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>1</v>
-      </c>
-      <c r="AK23">
-        <v>2</v>
-      </c>
-      <c r="AL23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3657,7 +3729,7 @@
         <v>2</v>
       </c>
       <c r="M24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -3681,10 +3753,10 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
@@ -3699,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="b">
         <v>0</v>
@@ -3717,10 +3789,10 @@
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3740,16 +3812,19 @@
       <c r="AN24">
         <v>0</v>
       </c>
+      <c r="AO24">
+        <v>42</v>
+      </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3767,10 +3842,10 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3785,19 +3860,19 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -3830,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3862,16 +3937,19 @@
       <c r="AN25">
         <v>0</v>
       </c>
+      <c r="AO25">
+        <v>36</v>
+      </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3925,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W26" t="b">
         <v>0</v>
@@ -3984,16 +4062,19 @@
       <c r="AN26">
         <v>0</v>
       </c>
+      <c r="AO26">
+        <v>29</v>
+      </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4041,16 +4122,16 @@
         <v>2</v>
       </c>
       <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>2</v>
+      </c>
+      <c r="V27">
         <v>4</v>
-      </c>
-      <c r="T27" t="b">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27">
-        <v>2</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
@@ -4083,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4106,16 +4187,19 @@
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>31</v>
+      </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4133,19 +4217,19 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -4169,10 +4253,10 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
@@ -4228,16 +4312,19 @@
       <c r="AN28">
         <v>0</v>
       </c>
+      <c r="AO28">
+        <v>31</v>
+      </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4246,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -4273,19 +4360,19 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -4309,78 +4396,81 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="b">
         <v>0</v>
       </c>
       <c r="AD29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="b">
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH29">
+        <v>3</v>
+      </c>
+      <c r="AI29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>2</v>
+      </c>
+      <c r="AL29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
         <v>4</v>
       </c>
-      <c r="AI29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>1</v>
-      </c>
-      <c r="AK29">
-        <v>2</v>
-      </c>
-      <c r="AL29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:40">
-      <c r="A30" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>151</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4404,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -4422,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
@@ -4440,10 +4530,10 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="b">
         <v>0</v>
@@ -4458,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="b">
         <v>1</v>
@@ -4472,16 +4562,19 @@
       <c r="AN30">
         <v>0</v>
       </c>
+      <c r="AO30">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4490,28 +4583,28 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>3</v>
+      </c>
+      <c r="M31">
         <v>4</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31">
-        <v>4</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>2</v>
-      </c>
-      <c r="M31">
-        <v>3</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -4594,16 +4687,19 @@
       <c r="AN31">
         <v>0</v>
       </c>
+      <c r="AO31">
+        <v>48</v>
+      </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4621,10 +4717,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4693,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4716,16 +4812,19 @@
       <c r="AN32">
         <v>0</v>
       </c>
+      <c r="AO32">
+        <v>45</v>
+      </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4734,28 +4833,28 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -4770,28 +4869,28 @@
         <v>0</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
+        <v>8</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>3</v>
+      </c>
+      <c r="V33">
         <v>5</v>
       </c>
-      <c r="T33" t="b">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>2</v>
-      </c>
-      <c r="V33">
-        <v>3</v>
-      </c>
       <c r="W33" t="b">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -4806,10 +4905,10 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
@@ -4824,10 +4923,10 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL33" t="b">
         <v>1</v>
@@ -4838,16 +4937,19 @@
       <c r="AN33">
         <v>0</v>
       </c>
+      <c r="AO33">
+        <v>45</v>
+      </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4856,28 +4958,28 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -4919,10 +5021,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC34" t="b">
         <v>0</v>
@@ -4960,16 +5062,19 @@
       <c r="AN34">
         <v>0</v>
       </c>
+      <c r="AO34">
+        <v>36</v>
+      </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:41">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -4978,19 +5083,19 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5041,10 +5146,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="b">
         <v>0</v>
@@ -5082,16 +5187,19 @@
       <c r="AN35">
         <v>0</v>
       </c>
+      <c r="AO35">
+        <v>38</v>
+      </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:41">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5109,19 +5217,19 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -5163,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC36" t="b">
         <v>0</v>
@@ -5204,16 +5312,19 @@
       <c r="AN36">
         <v>0</v>
       </c>
+      <c r="AO36">
+        <v>39</v>
+      </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:41">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5222,28 +5333,28 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -5285,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC37" t="b">
         <v>0</v>
@@ -5303,69 +5414,72 @@
         <v>0</v>
       </c>
       <c r="AG37">
+        <v>2</v>
+      </c>
+      <c r="AH37">
+        <v>3</v>
+      </c>
+      <c r="AI37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:41">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38">
         <v>4</v>
       </c>
-      <c r="AH37">
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
         <v>5</v>
       </c>
-      <c r="AI37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ37">
-        <v>1</v>
-      </c>
-      <c r="AK37">
-        <v>2</v>
-      </c>
-      <c r="AL37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:40">
-      <c r="A38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>2</v>
-      </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -5407,10 +5521,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="b">
         <v>0</v>
@@ -5425,10 +5539,10 @@
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5448,16 +5562,19 @@
       <c r="AN38">
         <v>0</v>
       </c>
+      <c r="AO38">
+        <v>44</v>
+      </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:41">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -5475,10 +5592,10 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5529,10 +5646,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="b">
         <v>0</v>
@@ -5570,16 +5687,19 @@
       <c r="AN39">
         <v>0</v>
       </c>
+      <c r="AO39">
+        <v>35</v>
+      </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:41">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5692,16 +5812,19 @@
       <c r="AN40">
         <v>0</v>
       </c>
+      <c r="AO40">
+        <v>37</v>
+      </c>
     </row>
-    <row r="41" spans="1:40">
+    <row r="41" spans="1:41">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5755,10 +5878,10 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="b">
         <v>0</v>
@@ -5814,16 +5937,19 @@
       <c r="AN41">
         <v>0</v>
       </c>
+      <c r="AO41">
+        <v>37</v>
+      </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:41">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -5835,43 +5961,43 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
@@ -5880,43 +6006,43 @@
         <v>1</v>
       </c>
       <c r="V42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" t="b">
         <v>0</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="b">
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF42" t="b">
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -5925,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="AK42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="b">
         <v>1</v>
@@ -5936,16 +6062,19 @@
       <c r="AN42">
         <v>0</v>
       </c>
+      <c r="AO42">
+        <v>36</v>
+      </c>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:41">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -6058,16 +6187,19 @@
       <c r="AN43">
         <v>0</v>
       </c>
+      <c r="AO43">
+        <v>11</v>
+      </c>
     </row>
-    <row r="44" spans="1:40">
+    <row r="44" spans="1:41">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -6079,239 +6211,245 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <v>1</v>
+      </c>
+      <c r="T44" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44">
+        <v>1</v>
+      </c>
+      <c r="W44" t="b">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>1</v>
+      </c>
+      <c r="AB44">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>1</v>
+      </c>
+      <c r="AE44">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>1</v>
+      </c>
+      <c r="AH44">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
+        <v>1</v>
+      </c>
+      <c r="AK44">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>0</v>
+      </c>
+      <c r="AO44">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:41">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>4</v>
       </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>2</v>
-      </c>
-      <c r="M44">
-        <v>3</v>
-      </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>2</v>
-      </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>3</v>
-      </c>
-      <c r="S44">
+      <c r="G45">
+        <v>12</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45">
         <v>4</v>
       </c>
-      <c r="T44" t="b">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>2</v>
-      </c>
-      <c r="V44">
-        <v>3</v>
-      </c>
-      <c r="W44" t="b">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>2</v>
-      </c>
-      <c r="Y44">
-        <v>3</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>2</v>
-      </c>
-      <c r="AB44">
-        <v>3</v>
-      </c>
-      <c r="AC44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>2</v>
-      </c>
-      <c r="AE44">
-        <v>3</v>
-      </c>
-      <c r="AF44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44">
-        <v>2</v>
-      </c>
-      <c r="AH44">
-        <v>3</v>
-      </c>
-      <c r="AI44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ44">
-        <v>1</v>
-      </c>
-      <c r="AK44">
-        <v>2</v>
-      </c>
-      <c r="AL44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
-        <v>0</v>
+      <c r="J45">
+        <v>12</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>4</v>
+      </c>
+      <c r="M45">
+        <v>12</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45">
+        <v>12</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>4</v>
+      </c>
+      <c r="S45">
+        <v>12</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>4</v>
+      </c>
+      <c r="V45">
+        <v>12</v>
+      </c>
+      <c r="W45" t="b">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>4</v>
+      </c>
+      <c r="Y45">
+        <v>12</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>4</v>
+      </c>
+      <c r="AB45">
+        <v>12</v>
+      </c>
+      <c r="AC45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>6</v>
+      </c>
+      <c r="AE45">
+        <v>12</v>
+      </c>
+      <c r="AF45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>4</v>
+      </c>
+      <c r="AH45">
+        <v>12</v>
+      </c>
+      <c r="AI45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>4</v>
+      </c>
+      <c r="AK45">
+        <v>12</v>
+      </c>
+      <c r="AL45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
-      <c r="A45" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>3</v>
-      </c>
-      <c r="J45">
-        <v>4</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>2</v>
-      </c>
-      <c r="M45">
-        <v>3</v>
-      </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>1</v>
-      </c>
-      <c r="P45">
-        <v>2</v>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>3</v>
-      </c>
-      <c r="S45">
-        <v>4</v>
-      </c>
-      <c r="T45" t="b">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>2</v>
-      </c>
-      <c r="V45">
-        <v>3</v>
-      </c>
-      <c r="W45" t="b">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>2</v>
-      </c>
-      <c r="Y45">
-        <v>3</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>2</v>
-      </c>
-      <c r="AB45">
-        <v>3</v>
-      </c>
-      <c r="AC45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>2</v>
-      </c>
-      <c r="AE45">
-        <v>3</v>
-      </c>
-      <c r="AF45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45">
-        <v>2</v>
-      </c>
-      <c r="AH45">
-        <v>3</v>
-      </c>
-      <c r="AI45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ45">
-        <v>1</v>
-      </c>
-      <c r="AK45">
-        <v>2</v>
-      </c>
-      <c r="AL45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM45">
-        <v>0</v>
-      </c>
-      <c r="AN45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:41">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -6424,16 +6562,19 @@
       <c r="AN46">
         <v>0</v>
       </c>
+      <c r="AO46">
+        <v>32</v>
+      </c>
     </row>
-    <row r="47" spans="1:40">
+    <row r="47" spans="1:41">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6546,16 +6687,19 @@
       <c r="AN47">
         <v>0</v>
       </c>
+      <c r="AO47">
+        <v>32</v>
+      </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:41">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6668,16 +6812,19 @@
       <c r="AN48">
         <v>0</v>
       </c>
+      <c r="AO48">
+        <v>32</v>
+      </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:41">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6695,19 +6842,19 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -6722,55 +6869,55 @@
         <v>0</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
       </c>
       <c r="U49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W49" t="b">
         <v>0</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="b">
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC49" t="b">
         <v>0</v>
       </c>
       <c r="AD49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -6790,118 +6937,121 @@
       <c r="AN49">
         <v>0</v>
       </c>
+      <c r="AO49">
+        <v>32</v>
+      </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:41">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+      <c r="J50">
         <v>4</v>
       </c>
-      <c r="G50">
-        <v>12</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50">
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>3</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
+        <v>2</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>3</v>
+      </c>
+      <c r="S50">
         <v>4</v>
       </c>
-      <c r="J50">
-        <v>12</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>4</v>
-      </c>
-      <c r="M50">
-        <v>12</v>
-      </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>4</v>
-      </c>
-      <c r="P50">
-        <v>12</v>
-      </c>
-      <c r="Q50" t="b">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>4</v>
-      </c>
-      <c r="S50">
-        <v>12</v>
-      </c>
       <c r="T50" t="b">
         <v>0</v>
       </c>
       <c r="U50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W50" t="b">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z50" t="b">
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC50" t="b">
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
       </c>
       <c r="AJ50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK50">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AL50" t="b">
         <v>1</v>
@@ -6912,13 +7062,16 @@
       <c r="AN50">
         <v>0</v>
       </c>
+      <c r="AO50">
+        <v>32</v>
+      </c>
     </row>
-    <row r="51" spans="1:40">
+    <row r="51" spans="1:41">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
         <v>154</v>
@@ -6939,10 +7092,10 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -6966,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T51" t="b">
         <v>0</v>
@@ -7034,16 +7187,19 @@
       <c r="AN51">
         <v>0</v>
       </c>
+      <c r="AO51">
+        <v>24</v>
+      </c>
     </row>
-    <row r="52" spans="1:40">
+    <row r="52" spans="1:41">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -7156,16 +7312,19 @@
       <c r="AN52">
         <v>0</v>
       </c>
+      <c r="AO52">
+        <v>21</v>
+      </c>
     </row>
-    <row r="53" spans="1:40">
+    <row r="53" spans="1:41">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7278,16 +7437,19 @@
       <c r="AN53">
         <v>0</v>
       </c>
+      <c r="AO53">
+        <v>21</v>
+      </c>
     </row>
-    <row r="54" spans="1:40">
+    <row r="54" spans="1:41">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7400,16 +7562,19 @@
       <c r="AN54">
         <v>0</v>
       </c>
+      <c r="AO54">
+        <v>21</v>
+      </c>
     </row>
-    <row r="55" spans="1:40">
+    <row r="55" spans="1:41">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7418,100 +7583,100 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
       </c>
       <c r="O55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="b">
         <v>0</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" t="b">
         <v>0</v>
       </c>
       <c r="X55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="b">
         <v>0</v>
       </c>
       <c r="AD55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="b">
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI55" t="b">
         <v>0</v>
       </c>
       <c r="AJ55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL55" t="b">
         <v>1</v>
@@ -7521,6 +7686,9 @@
       </c>
       <c r="AN55">
         <v>0</v>
+      </c>
+      <c r="AO55">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
+++ b/Data/Rules/Bradley Caldwell Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="158">
   <si>
     <t>SKU</t>
   </si>
@@ -301,6 +301,9 @@
     <t>29744</t>
   </si>
   <si>
+    <t>14293</t>
+  </si>
+  <si>
     <t>BBB Dipped Cow Ear Bacon</t>
   </si>
   <si>
@@ -461,6 +464,9 @@
   </si>
   <si>
     <t>Wee-Wee Disposable Diapers XS 12ct</t>
+  </si>
+  <si>
+    <t>Canidae Pure Bison 4lb</t>
   </si>
   <si>
     <t>Bradley Caldwell</t>
@@ -813,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:41">
@@ -946,10 +952,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -1071,10 +1077,10 @@
         <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -1196,10 +1202,10 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -1321,10 +1327,10 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5">
         <v>25</v>
@@ -1446,10 +1452,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -1571,10 +1577,10 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -1696,10 +1702,10 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8">
         <v>25</v>
@@ -1821,10 +1827,10 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9">
         <v>20</v>
@@ -1946,10 +1952,10 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2071,10 +2077,10 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2196,10 +2202,10 @@
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2321,10 +2327,10 @@
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2446,10 +2452,10 @@
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2571,10 +2577,10 @@
         <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2696,10 +2702,10 @@
         <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2821,10 +2827,10 @@
         <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2946,10 +2952,10 @@
         <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3071,10 +3077,10 @@
         <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3196,10 +3202,10 @@
         <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3321,10 +3327,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3446,10 +3452,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3571,10 +3577,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3696,10 +3702,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3821,10 +3827,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3946,10 +3952,10 @@
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -4071,10 +4077,10 @@
         <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4196,10 +4202,10 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4321,10 +4327,10 @@
         <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4446,10 +4452,10 @@
         <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4571,10 +4577,10 @@
         <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4696,10 +4702,10 @@
         <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4821,10 +4827,10 @@
         <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4946,10 +4952,10 @@
         <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -5071,10 +5077,10 @@
         <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -5196,10 +5202,10 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5321,10 +5327,10 @@
         <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5446,10 +5452,10 @@
         <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -5571,10 +5577,10 @@
         <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -5696,10 +5702,10 @@
         <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5821,10 +5827,10 @@
         <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5946,10 +5952,10 @@
         <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -6071,10 +6077,10 @@
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -6196,10 +6202,10 @@
         <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -6321,10 +6327,10 @@
         <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D45">
         <v>12</v>
@@ -6446,10 +6452,10 @@
         <v>85</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -6571,10 +6577,10 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6696,10 +6702,10 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6821,10 +6827,10 @@
         <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6946,10 +6952,10 @@
         <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -7071,10 +7077,10 @@
         <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -7196,10 +7202,10 @@
         <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -7321,10 +7327,10 @@
         <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7446,10 +7452,10 @@
         <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7571,10 +7577,10 @@
         <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7689,6 +7695,131 @@
       </c>
       <c r="AO55">
         <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:41">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56" t="b">
+        <v>1</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56" t="b">
+        <v>1</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
+        <v>0</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
